--- a/Database/mau_chuan.xlsx
+++ b/Database/mau_chuan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>?Entity_Line1</t>
   </si>
@@ -192,6 +192,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -200,9 +203,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,50 +505,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -557,132 +555,60 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -693,12 +619,12 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -716,5 +642,6 @@
     <mergeCell ref="H13:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>